--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1692,6 +1692,18 @@
         </is>
       </c>
       <c r="B40" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:14:40</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1704,6 +1704,18 @@
         </is>
       </c>
       <c r="B41" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-21 19:01:01</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1716,6 +1716,18 @@
         </is>
       </c>
       <c r="B42" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-22 17:53:14</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1728,6 +1728,18 @@
         </is>
       </c>
       <c r="B43" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-23 18:11:06</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1740,6 +1740,18 @@
         </is>
       </c>
       <c r="B44" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-24 18:06:35</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,6 +1752,18 @@
         </is>
       </c>
       <c r="B45" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-25 18:11:24</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1764,6 +1764,18 @@
         </is>
       </c>
       <c r="B46" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-26 17:35:02</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1776,6 +1776,18 @@
         </is>
       </c>
       <c r="B47" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-27 18:01:15</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1788,6 +1788,18 @@
         </is>
       </c>
       <c r="B48" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-28 20:20:59</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1800,6 +1800,18 @@
         </is>
       </c>
       <c r="B49" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-29 19:04:49</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1812,6 +1812,18 @@
         </is>
       </c>
       <c r="B50" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-30 18:46:51</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1824,6 +1824,18 @@
         </is>
       </c>
       <c r="B51" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-20 18:16:06</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1836,6 +1836,18 @@
         </is>
       </c>
       <c r="B52" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-21 18:20:06</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1848,6 +1848,18 @@
         </is>
       </c>
       <c r="B53" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-22 18:14:14</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B54"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1860,6 +1860,18 @@
         </is>
       </c>
       <c r="B54" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-23 18:03:47</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B55"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1872,6 +1872,18 @@
         </is>
       </c>
       <c r="B55" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-10-24 17:09:38</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1884,6 +1884,18 @@
         </is>
       </c>
       <c r="B56" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-25 17:21:55</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B57"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1896,6 +1896,18 @@
         </is>
       </c>
       <c r="B57" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-26 19:41:39</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1908,6 +1908,18 @@
         </is>
       </c>
       <c r="B58" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-10-27 19:10:23</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1920,6 +1920,18 @@
         </is>
       </c>
       <c r="B59" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-10-28 19:16:45</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1932,6 +1932,18 @@
         </is>
       </c>
       <c r="B60" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-29 19:23:02</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B61"/>
+  <dimension ref="A1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1944,6 +1944,18 @@
         </is>
       </c>
       <c r="B61" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-10-30 18:56:58</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>
